--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127822938</v>
       </c>
       <c r="B2" t="n">
-        <v>95783</v>
+        <v>95789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127822929</v>
       </c>
       <c r="B4" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127822932</v>
       </c>
       <c r="B5" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127822933</v>
       </c>
       <c r="B8" t="n">
-        <v>90836</v>
+        <v>90842</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127822927</v>
       </c>
       <c r="B10" t="n">
-        <v>90809</v>
+        <v>90815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127822930</v>
       </c>
       <c r="B11" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127822928</v>
       </c>
       <c r="B12" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>127822936</v>
       </c>
       <c r="B13" t="n">
-        <v>95781</v>
+        <v>95787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>127822931</v>
       </c>
       <c r="B14" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,6 +1945,1094 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127847537</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>634222</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6659810</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127847524</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>634229</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6659801</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127847511</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91792</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>634202</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6659850</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Intorkad på liggande gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127847536</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92008</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>898</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>634214</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6659848</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127847540</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91391</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>634239</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6659810</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127847519</v>
+      </c>
+      <c r="B20" t="n">
+        <v>95787</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>634194</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6659965</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127847526</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>634229</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6659844</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127847522</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>634236</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6659806</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>15 bladrosette</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127847539</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91391</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>634243</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6659820</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127847513</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91338</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>634214</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6659847</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127847528</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>634243</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6659813</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>40 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127822938</v>
       </c>
       <c r="B2" t="n">
-        <v>95789</v>
+        <v>95792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127822935</v>
       </c>
       <c r="B3" t="n">
-        <v>80336</v>
+        <v>80339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127822929</v>
       </c>
       <c r="B4" t="n">
-        <v>96708</v>
+        <v>96711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127822932</v>
       </c>
       <c r="B5" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127822940</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127822933</v>
       </c>
       <c r="B8" t="n">
-        <v>90842</v>
+        <v>90845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127822927</v>
       </c>
       <c r="B10" t="n">
-        <v>90815</v>
+        <v>90818</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127822930</v>
       </c>
       <c r="B11" t="n">
-        <v>96708</v>
+        <v>96711</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127822928</v>
       </c>
       <c r="B12" t="n">
-        <v>96708</v>
+        <v>96711</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>127822936</v>
       </c>
       <c r="B13" t="n">
-        <v>95787</v>
+        <v>95790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>127822931</v>
       </c>
       <c r="B14" t="n">
-        <v>96708</v>
+        <v>96711</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127847524</v>
+        <v>127847511</v>
       </c>
       <c r="B16" t="n">
-        <v>98456</v>
+        <v>91795</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2056,34 +2056,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634229</v>
+        <v>634202</v>
       </c>
       <c r="R16" t="n">
-        <v>6659801</v>
+        <v>6659850</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2118,12 +2121,18 @@
           <t>2025-08-26</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Intorkad på liggande gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2142,10 +2151,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127847511</v>
+        <v>127847524</v>
       </c>
       <c r="B17" t="n">
-        <v>91792</v>
+        <v>98459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2153,37 +2162,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634202</v>
+        <v>634229</v>
       </c>
       <c r="R17" t="n">
-        <v>6659850</v>
+        <v>6659801</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2218,18 +2224,12 @@
           <t>2025-08-26</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Intorkad på liggande gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>127847536</v>
       </c>
       <c r="B18" t="n">
-        <v>92008</v>
+        <v>92011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>127847540</v>
       </c>
       <c r="B19" t="n">
-        <v>91391</v>
+        <v>91394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>127847519</v>
       </c>
       <c r="B20" t="n">
-        <v>95787</v>
+        <v>95790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>127847526</v>
       </c>
       <c r="B21" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>127847522</v>
       </c>
       <c r="B22" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>127847539</v>
       </c>
       <c r="B23" t="n">
-        <v>91391</v>
+        <v>91394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127847513</v>
+        <v>127847528</v>
       </c>
       <c r="B24" t="n">
-        <v>91338</v>
+        <v>98459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>634214</v>
+        <v>634243</v>
       </c>
       <c r="R24" t="n">
-        <v>6659847</v>
+        <v>6659813</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2908,6 +2908,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>40 bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2934,32 +2939,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127847528</v>
+        <v>127847513</v>
       </c>
       <c r="B25" t="n">
-        <v>98456</v>
+        <v>91341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2969,10 +2974,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>634243</v>
+        <v>634214</v>
       </c>
       <c r="R25" t="n">
-        <v>6659813</v>
+        <v>6659847</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3005,11 +3010,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>40 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127822938</v>
       </c>
       <c r="B2" t="n">
-        <v>95792</v>
+        <v>95800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127822935</v>
       </c>
       <c r="B3" t="n">
-        <v>80339</v>
+        <v>80345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127822929</v>
       </c>
       <c r="B4" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127822932</v>
       </c>
       <c r="B5" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127822940</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127822933</v>
       </c>
       <c r="B8" t="n">
-        <v>90845</v>
+        <v>90853</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127822927</v>
       </c>
       <c r="B10" t="n">
-        <v>90818</v>
+        <v>90826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127822930</v>
       </c>
       <c r="B11" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127822928</v>
       </c>
       <c r="B12" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>127822936</v>
       </c>
       <c r="B13" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>127822931</v>
       </c>
       <c r="B14" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127847511</v>
+        <v>127847524</v>
       </c>
       <c r="B16" t="n">
-        <v>91795</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2056,37 +2056,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634202</v>
+        <v>634229</v>
       </c>
       <c r="R16" t="n">
-        <v>6659850</v>
+        <v>6659801</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2121,18 +2118,12 @@
           <t>2025-08-26</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Intorkad på liggande gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2151,10 +2142,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127847524</v>
+        <v>127847511</v>
       </c>
       <c r="B17" t="n">
-        <v>98459</v>
+        <v>91803</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2162,34 +2153,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634229</v>
+        <v>634202</v>
       </c>
       <c r="R17" t="n">
-        <v>6659801</v>
+        <v>6659850</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2224,12 +2218,18 @@
           <t>2025-08-26</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Intorkad på liggande gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>127847536</v>
       </c>
       <c r="B18" t="n">
-        <v>92011</v>
+        <v>92019</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>127847540</v>
       </c>
       <c r="B19" t="n">
-        <v>91394</v>
+        <v>91402</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>127847519</v>
       </c>
       <c r="B20" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>127847526</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>127847522</v>
       </c>
       <c r="B22" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>127847539</v>
       </c>
       <c r="B23" t="n">
-        <v>91394</v>
+        <v>91402</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127847528</v>
+        <v>127847513</v>
       </c>
       <c r="B24" t="n">
-        <v>98459</v>
+        <v>91349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>634243</v>
+        <v>634214</v>
       </c>
       <c r="R24" t="n">
-        <v>6659813</v>
+        <v>6659847</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2908,11 +2908,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>40 bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2939,32 +2934,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127847513</v>
+        <v>127847528</v>
       </c>
       <c r="B25" t="n">
-        <v>91341</v>
+        <v>98467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2974,10 +2969,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>634214</v>
+        <v>634243</v>
       </c>
       <c r="R25" t="n">
-        <v>6659847</v>
+        <v>6659813</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3010,6 +3005,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>40 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127822938</v>
       </c>
       <c r="B2" t="n">
-        <v>95800</v>
+        <v>95801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127822929</v>
       </c>
       <c r="B4" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127822932</v>
       </c>
       <c r="B5" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127822933</v>
       </c>
       <c r="B8" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127822927</v>
       </c>
       <c r="B10" t="n">
-        <v>90826</v>
+        <v>90827</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127822930</v>
       </c>
       <c r="B11" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127822928</v>
       </c>
       <c r="B12" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>127822936</v>
       </c>
       <c r="B13" t="n">
-        <v>95798</v>
+        <v>95799</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>127822931</v>
       </c>
       <c r="B14" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127847524</v>
+        <v>127847511</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>91804</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2056,34 +2056,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634229</v>
+        <v>634202</v>
       </c>
       <c r="R16" t="n">
-        <v>6659801</v>
+        <v>6659850</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2118,12 +2121,18 @@
           <t>2025-08-26</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Intorkad på liggande gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2142,10 +2151,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127847511</v>
+        <v>127847524</v>
       </c>
       <c r="B17" t="n">
-        <v>91803</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2153,37 +2162,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634202</v>
+        <v>634229</v>
       </c>
       <c r="R17" t="n">
-        <v>6659850</v>
+        <v>6659801</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2218,18 +2224,12 @@
           <t>2025-08-26</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Intorkad på liggande gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>127847536</v>
       </c>
       <c r="B18" t="n">
-        <v>92019</v>
+        <v>92020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>127847540</v>
       </c>
       <c r="B19" t="n">
-        <v>91402</v>
+        <v>91403</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>127847519</v>
       </c>
       <c r="B20" t="n">
-        <v>95798</v>
+        <v>95799</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>127847526</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>127847522</v>
       </c>
       <c r="B22" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>127847539</v>
       </c>
       <c r="B23" t="n">
-        <v>91402</v>
+        <v>91403</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>127847513</v>
       </c>
       <c r="B24" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>127847528</v>
       </c>
       <c r="B25" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127822938</v>
       </c>
       <c r="B2" t="n">
-        <v>95801</v>
+        <v>95802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127822929</v>
       </c>
       <c r="B4" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127822932</v>
       </c>
       <c r="B5" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127822933</v>
       </c>
       <c r="B8" t="n">
-        <v>90854</v>
+        <v>90855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127822927</v>
       </c>
       <c r="B10" t="n">
-        <v>90827</v>
+        <v>90828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127822930</v>
       </c>
       <c r="B11" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127822928</v>
       </c>
       <c r="B12" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>127822936</v>
       </c>
       <c r="B13" t="n">
-        <v>95799</v>
+        <v>95800</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>127822931</v>
       </c>
       <c r="B14" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127847511</v>
+        <v>127847524</v>
       </c>
       <c r="B16" t="n">
-        <v>91804</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2056,37 +2056,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634202</v>
+        <v>634229</v>
       </c>
       <c r="R16" t="n">
-        <v>6659850</v>
+        <v>6659801</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2121,18 +2118,12 @@
           <t>2025-08-26</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Intorkad på liggande gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2151,10 +2142,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127847524</v>
+        <v>127847511</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>91805</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2162,34 +2153,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634229</v>
+        <v>634202</v>
       </c>
       <c r="R17" t="n">
-        <v>6659801</v>
+        <v>6659850</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2224,12 +2218,18 @@
           <t>2025-08-26</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Intorkad på liggande gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>127847536</v>
       </c>
       <c r="B18" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>127847540</v>
       </c>
       <c r="B19" t="n">
-        <v>91403</v>
+        <v>91404</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>127847519</v>
       </c>
       <c r="B20" t="n">
-        <v>95799</v>
+        <v>95800</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>127847526</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>127847522</v>
       </c>
       <c r="B22" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>127847539</v>
       </c>
       <c r="B23" t="n">
-        <v>91403</v>
+        <v>91404</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>127847513</v>
       </c>
       <c r="B24" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>127847528</v>
       </c>
       <c r="B25" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127822938</v>
       </c>
       <c r="B2" t="n">
-        <v>95802</v>
+        <v>95803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127822929</v>
       </c>
       <c r="B4" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127822932</v>
       </c>
       <c r="B5" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127822933</v>
       </c>
       <c r="B8" t="n">
-        <v>90855</v>
+        <v>90856</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127822927</v>
       </c>
       <c r="B10" t="n">
-        <v>90828</v>
+        <v>90829</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127822930</v>
       </c>
       <c r="B11" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127822928</v>
       </c>
       <c r="B12" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>127822936</v>
       </c>
       <c r="B13" t="n">
-        <v>95800</v>
+        <v>95801</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>127822931</v>
       </c>
       <c r="B14" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>127847524</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>127847511</v>
       </c>
       <c r="B17" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>127847536</v>
       </c>
       <c r="B18" t="n">
-        <v>92021</v>
+        <v>92022</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>127847540</v>
       </c>
       <c r="B19" t="n">
-        <v>91404</v>
+        <v>91405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>127847519</v>
       </c>
       <c r="B20" t="n">
-        <v>95800</v>
+        <v>95801</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>127847526</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>127847522</v>
       </c>
       <c r="B22" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>127847539</v>
       </c>
       <c r="B23" t="n">
-        <v>91404</v>
+        <v>91405</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>127847513</v>
       </c>
       <c r="B24" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>127847528</v>
       </c>
       <c r="B25" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -2045,10 +2045,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127847524</v>
+        <v>127847511</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>91806</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2056,34 +2056,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634229</v>
+        <v>634202</v>
       </c>
       <c r="R16" t="n">
-        <v>6659801</v>
+        <v>6659850</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2118,12 +2121,18 @@
           <t>2025-08-26</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Intorkad på liggande gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2142,10 +2151,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127847511</v>
+        <v>127847524</v>
       </c>
       <c r="B17" t="n">
-        <v>91806</v>
+        <v>98470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2153,37 +2162,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634202</v>
+        <v>634229</v>
       </c>
       <c r="R17" t="n">
-        <v>6659850</v>
+        <v>6659801</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2218,18 +2224,12 @@
           <t>2025-08-26</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Intorkad på liggande gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -2045,10 +2045,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127847511</v>
+        <v>127847524</v>
       </c>
       <c r="B16" t="n">
-        <v>91806</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2056,37 +2056,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634202</v>
+        <v>634229</v>
       </c>
       <c r="R16" t="n">
-        <v>6659850</v>
+        <v>6659801</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2121,18 +2118,12 @@
           <t>2025-08-26</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Intorkad på liggande gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2151,10 +2142,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127847524</v>
+        <v>127847511</v>
       </c>
       <c r="B17" t="n">
-        <v>98470</v>
+        <v>91806</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2162,34 +2153,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634229</v>
+        <v>634202</v>
       </c>
       <c r="R17" t="n">
-        <v>6659801</v>
+        <v>6659850</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2224,12 +2218,18 @@
           <t>2025-08-26</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Intorkad på liggande gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127822938</v>
       </c>
       <c r="B2" t="n">
-        <v>95803</v>
+        <v>95811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127822935</v>
       </c>
       <c r="B3" t="n">
-        <v>80345</v>
+        <v>80348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127822929</v>
       </c>
       <c r="B4" t="n">
-        <v>96722</v>
+        <v>96730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127822932</v>
       </c>
       <c r="B5" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127822940</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127822933</v>
       </c>
       <c r="B8" t="n">
-        <v>90856</v>
+        <v>90862</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127822927</v>
       </c>
       <c r="B10" t="n">
-        <v>90829</v>
+        <v>90835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127822930</v>
       </c>
       <c r="B11" t="n">
-        <v>96722</v>
+        <v>96730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127822928</v>
       </c>
       <c r="B12" t="n">
-        <v>96722</v>
+        <v>96730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>127822936</v>
       </c>
       <c r="B13" t="n">
-        <v>95801</v>
+        <v>95809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>127822931</v>
       </c>
       <c r="B14" t="n">
-        <v>96722</v>
+        <v>96730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>127847524</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>127847511</v>
       </c>
       <c r="B17" t="n">
-        <v>91806</v>
+        <v>91814</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>127847536</v>
       </c>
       <c r="B18" t="n">
-        <v>92022</v>
+        <v>92030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>127847540</v>
       </c>
       <c r="B19" t="n">
-        <v>91405</v>
+        <v>91413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>127847519</v>
       </c>
       <c r="B20" t="n">
-        <v>95801</v>
+        <v>95809</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>127847526</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>127847522</v>
       </c>
       <c r="B22" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>127847539</v>
       </c>
       <c r="B23" t="n">
-        <v>91405</v>
+        <v>91413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127847513</v>
+        <v>127847528</v>
       </c>
       <c r="B24" t="n">
-        <v>91352</v>
+        <v>98478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>634214</v>
+        <v>634243</v>
       </c>
       <c r="R24" t="n">
-        <v>6659847</v>
+        <v>6659813</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2908,6 +2908,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>40 bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2934,32 +2939,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127847528</v>
+        <v>127847513</v>
       </c>
       <c r="B25" t="n">
-        <v>98470</v>
+        <v>91360</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2969,10 +2974,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>634243</v>
+        <v>634214</v>
       </c>
       <c r="R25" t="n">
-        <v>6659813</v>
+        <v>6659847</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3005,11 +3010,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>40 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -2045,10 +2045,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127847524</v>
+        <v>127847511</v>
       </c>
       <c r="B16" t="n">
-        <v>98478</v>
+        <v>91814</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2056,34 +2056,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634229</v>
+        <v>634202</v>
       </c>
       <c r="R16" t="n">
-        <v>6659801</v>
+        <v>6659850</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2118,12 +2121,18 @@
           <t>2025-08-26</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Intorkad på liggande gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2142,10 +2151,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127847511</v>
+        <v>127847524</v>
       </c>
       <c r="B17" t="n">
-        <v>91814</v>
+        <v>98478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2153,37 +2162,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634202</v>
+        <v>634229</v>
       </c>
       <c r="R17" t="n">
-        <v>6659850</v>
+        <v>6659801</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2218,18 +2224,12 @@
           <t>2025-08-26</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Intorkad på liggande gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127822938</v>
       </c>
       <c r="B2" t="n">
-        <v>95811</v>
+        <v>95904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127822935</v>
       </c>
       <c r="B3" t="n">
-        <v>80348</v>
+        <v>80406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127822929</v>
       </c>
       <c r="B4" t="n">
-        <v>96730</v>
+        <v>96823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127822932</v>
       </c>
       <c r="B5" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127822940</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127822933</v>
       </c>
       <c r="B8" t="n">
-        <v>90862</v>
+        <v>90954</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127822927</v>
       </c>
       <c r="B10" t="n">
-        <v>90835</v>
+        <v>90927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127822930</v>
       </c>
       <c r="B11" t="n">
-        <v>96730</v>
+        <v>96823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127822928</v>
       </c>
       <c r="B12" t="n">
-        <v>96730</v>
+        <v>96823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>127822936</v>
       </c>
       <c r="B13" t="n">
-        <v>95809</v>
+        <v>95902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>127822931</v>
       </c>
       <c r="B14" t="n">
-        <v>96730</v>
+        <v>96823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>127847511</v>
       </c>
       <c r="B16" t="n">
-        <v>91814</v>
+        <v>91906</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>127847524</v>
       </c>
       <c r="B17" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>127847536</v>
       </c>
       <c r="B18" t="n">
-        <v>92030</v>
+        <v>92122</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>127847540</v>
       </c>
       <c r="B19" t="n">
-        <v>91413</v>
+        <v>91505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>127847519</v>
       </c>
       <c r="B20" t="n">
-        <v>95809</v>
+        <v>95902</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>127847526</v>
       </c>
       <c r="B21" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>127847522</v>
       </c>
       <c r="B22" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>127847539</v>
       </c>
       <c r="B23" t="n">
-        <v>91413</v>
+        <v>91505</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127847528</v>
+        <v>127847513</v>
       </c>
       <c r="B24" t="n">
-        <v>98478</v>
+        <v>91452</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>634243</v>
+        <v>634214</v>
       </c>
       <c r="R24" t="n">
-        <v>6659813</v>
+        <v>6659847</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2908,11 +2908,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>40 bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2939,32 +2934,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127847513</v>
+        <v>127847528</v>
       </c>
       <c r="B25" t="n">
-        <v>91360</v>
+        <v>98571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2974,10 +2969,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>634214</v>
+        <v>634243</v>
       </c>
       <c r="R25" t="n">
-        <v>6659847</v>
+        <v>6659813</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3010,6 +3005,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>40 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -2837,32 +2837,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127847513</v>
+        <v>127847528</v>
       </c>
       <c r="B24" t="n">
-        <v>91452</v>
+        <v>98571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>634214</v>
+        <v>634243</v>
       </c>
       <c r="R24" t="n">
-        <v>6659847</v>
+        <v>6659813</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2908,6 +2908,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>40 bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2934,32 +2939,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127847528</v>
+        <v>127847513</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>91452</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2969,10 +2974,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>634243</v>
+        <v>634214</v>
       </c>
       <c r="R25" t="n">
-        <v>6659813</v>
+        <v>6659847</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3005,11 +3010,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>40 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -2045,10 +2045,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127847511</v>
+        <v>127847524</v>
       </c>
       <c r="B16" t="n">
-        <v>91906</v>
+        <v>98571</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2056,37 +2056,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634202</v>
+        <v>634229</v>
       </c>
       <c r="R16" t="n">
-        <v>6659850</v>
+        <v>6659801</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2121,18 +2118,12 @@
           <t>2025-08-26</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Intorkad på liggande gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2151,10 +2142,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127847524</v>
+        <v>127847511</v>
       </c>
       <c r="B17" t="n">
-        <v>98571</v>
+        <v>91906</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2162,34 +2153,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634229</v>
+        <v>634202</v>
       </c>
       <c r="R17" t="n">
-        <v>6659801</v>
+        <v>6659850</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2224,12 +2218,18 @@
           <t>2025-08-26</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Intorkad på liggande gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -2048,7 +2048,7 @@
         <v>127847524</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>127847511</v>
       </c>
       <c r="B17" t="n">
-        <v>91906</v>
+        <v>91918</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>127847536</v>
       </c>
       <c r="B18" t="n">
-        <v>92122</v>
+        <v>92134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>127847540</v>
       </c>
       <c r="B19" t="n">
-        <v>91505</v>
+        <v>91517</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>127847519</v>
       </c>
       <c r="B20" t="n">
-        <v>95902</v>
+        <v>95914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>127847526</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>127847522</v>
       </c>
       <c r="B22" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>127847539</v>
       </c>
       <c r="B23" t="n">
-        <v>91505</v>
+        <v>91517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,32 +2837,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127847528</v>
+        <v>127847513</v>
       </c>
       <c r="B24" t="n">
-        <v>98571</v>
+        <v>91464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>634243</v>
+        <v>634214</v>
       </c>
       <c r="R24" t="n">
-        <v>6659813</v>
+        <v>6659847</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2908,11 +2908,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>40 bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2939,32 +2934,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127847513</v>
+        <v>127847528</v>
       </c>
       <c r="B25" t="n">
-        <v>91452</v>
+        <v>98585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2974,10 +2969,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>634214</v>
+        <v>634243</v>
       </c>
       <c r="R25" t="n">
-        <v>6659847</v>
+        <v>6659813</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3010,6 +3005,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>40 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3034,6 +3034,297 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129408823</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>633912</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6660074</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129408822</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>634152</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6659919</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129408824</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>634203</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6659855</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>129408823</v>
       </c>
       <c r="B26" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129408822</v>
       </c>
       <c r="B27" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>129408824</v>
       </c>
       <c r="B28" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>129408823</v>
       </c>
       <c r="B26" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129408822</v>
       </c>
       <c r="B27" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>129408824</v>
       </c>
       <c r="B28" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>129408823</v>
       </c>
       <c r="B26" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129408822</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>129408824</v>
       </c>
       <c r="B28" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>129408823</v>
       </c>
       <c r="B26" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129408822</v>
       </c>
       <c r="B27" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>129408824</v>
       </c>
       <c r="B28" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>129408823</v>
       </c>
       <c r="B26" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129408822</v>
       </c>
       <c r="B27" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>129408824</v>
       </c>
       <c r="B28" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>129408823</v>
       </c>
       <c r="B26" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129408822</v>
       </c>
       <c r="B27" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>129408824</v>
       </c>
       <c r="B28" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>129408823</v>
       </c>
       <c r="B26" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129408822</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>129408824</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>129408823</v>
       </c>
       <c r="B26" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129408822</v>
       </c>
       <c r="B27" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>129408824</v>
       </c>
       <c r="B28" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>129408823</v>
       </c>
       <c r="B26" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129408822</v>
       </c>
       <c r="B27" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>129408824</v>
       </c>
       <c r="B28" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>129408823</v>
       </c>
       <c r="B26" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129408822</v>
       </c>
       <c r="B27" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>129408824</v>
       </c>
       <c r="B28" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>129408823</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129408822</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>129408824</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>129408823</v>
       </c>
       <c r="B26" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129408822</v>
       </c>
       <c r="B27" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>129408824</v>
       </c>
       <c r="B28" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3325,6 +3325,802 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129963923</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97665</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>634194</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6659850</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129963932</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>634159</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6659902</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129963925</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97665</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>634068</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6660027</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129963931</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>633898</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6660073</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129963922</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92055</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>634101</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6659953</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129963930</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>634153</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6659918</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>30 buketter</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129963929</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>633905</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6660069</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>7 buketter</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129963904</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>633920</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6660072</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3327,32 +3327,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129963923</v>
+        <v>129963932</v>
       </c>
       <c r="B29" t="n">
-        <v>97665</v>
+        <v>98794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>634194</v>
+        <v>634159</v>
       </c>
       <c r="R29" t="n">
-        <v>6659850</v>
+        <v>6659902</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3398,6 +3398,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3424,32 +3429,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129963932</v>
+        <v>129963923</v>
       </c>
       <c r="B30" t="n">
-        <v>98794</v>
+        <v>97665</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3459,10 +3464,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>634159</v>
+        <v>634194</v>
       </c>
       <c r="R30" t="n">
-        <v>6659902</v>
+        <v>6659850</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3495,11 +3500,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3330,7 +3330,7 @@
         <v>129963932</v>
       </c>
       <c r="B29" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>129963923</v>
       </c>
       <c r="B30" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>129963925</v>
       </c>
       <c r="B31" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>129963931</v>
       </c>
       <c r="B32" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>129963922</v>
       </c>
       <c r="B33" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>129963930</v>
       </c>
       <c r="B34" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>129963929</v>
       </c>
       <c r="B35" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3330,7 +3330,7 @@
         <v>129963932</v>
       </c>
       <c r="B29" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>129963923</v>
       </c>
       <c r="B30" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>129963925</v>
       </c>
       <c r="B31" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>129963931</v>
       </c>
       <c r="B32" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>129963922</v>
       </c>
       <c r="B33" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>129963930</v>
       </c>
       <c r="B34" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>129963929</v>
       </c>
       <c r="B35" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3327,32 +3327,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129963932</v>
+        <v>129963923</v>
       </c>
       <c r="B29" t="n">
-        <v>98798</v>
+        <v>97686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>634159</v>
+        <v>634194</v>
       </c>
       <c r="R29" t="n">
-        <v>6659902</v>
+        <v>6659850</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3398,11 +3398,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3429,32 +3424,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129963923</v>
+        <v>129963932</v>
       </c>
       <c r="B30" t="n">
-        <v>97669</v>
+        <v>98815</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3464,10 +3459,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>634194</v>
+        <v>634159</v>
       </c>
       <c r="R30" t="n">
-        <v>6659850</v>
+        <v>6659902</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3500,6 +3495,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3529,7 +3529,7 @@
         <v>129963925</v>
       </c>
       <c r="B31" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>129963931</v>
       </c>
       <c r="B32" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>129963922</v>
       </c>
       <c r="B33" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>129963930</v>
       </c>
       <c r="B34" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>129963929</v>
       </c>
       <c r="B35" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3327,32 +3327,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129963923</v>
+        <v>129963932</v>
       </c>
       <c r="B29" t="n">
-        <v>97702</v>
+        <v>98831</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>634194</v>
+        <v>634159</v>
       </c>
       <c r="R29" t="n">
-        <v>6659850</v>
+        <v>6659902</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3398,6 +3398,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3424,32 +3429,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129963932</v>
+        <v>129963923</v>
       </c>
       <c r="B30" t="n">
-        <v>98831</v>
+        <v>97702</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3459,10 +3464,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>634159</v>
+        <v>634194</v>
       </c>
       <c r="R30" t="n">
-        <v>6659902</v>
+        <v>6659850</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3495,11 +3500,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3327,32 +3327,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129963932</v>
+        <v>129963923</v>
       </c>
       <c r="B29" t="n">
-        <v>98831</v>
+        <v>97704</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>634159</v>
+        <v>634194</v>
       </c>
       <c r="R29" t="n">
-        <v>6659902</v>
+        <v>6659850</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3398,11 +3398,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3429,32 +3424,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129963923</v>
+        <v>129963932</v>
       </c>
       <c r="B30" t="n">
-        <v>97702</v>
+        <v>98833</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3464,10 +3459,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>634194</v>
+        <v>634159</v>
       </c>
       <c r="R30" t="n">
-        <v>6659850</v>
+        <v>6659902</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3500,6 +3495,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3529,7 +3529,7 @@
         <v>129963925</v>
       </c>
       <c r="B31" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>129963931</v>
       </c>
       <c r="B32" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>129963922</v>
       </c>
       <c r="B33" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>129963930</v>
       </c>
       <c r="B34" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>129963929</v>
       </c>
       <c r="B35" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -3327,32 +3327,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129963923</v>
+        <v>129963932</v>
       </c>
       <c r="B29" t="n">
-        <v>97704</v>
+        <v>98920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>634194</v>
+        <v>634159</v>
       </c>
       <c r="R29" t="n">
-        <v>6659850</v>
+        <v>6659902</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3398,6 +3398,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3424,32 +3429,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129963932</v>
+        <v>129963923</v>
       </c>
       <c r="B30" t="n">
-        <v>98833</v>
+        <v>97791</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3459,10 +3464,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>634159</v>
+        <v>634194</v>
       </c>
       <c r="R30" t="n">
-        <v>6659902</v>
+        <v>6659850</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3495,11 +3500,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3529,7 +3529,7 @@
         <v>129963925</v>
       </c>
       <c r="B31" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>129963931</v>
       </c>
       <c r="B32" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>129963922</v>
       </c>
       <c r="B33" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>129963930</v>
       </c>
       <c r="B34" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>129963929</v>
       </c>
       <c r="B35" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -4126,7 +4126,7 @@
         <v>131934890</v>
       </c>
       <c r="B37" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>131934895</v>
       </c>
       <c r="B38" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>131934964</v>
       </c>
       <c r="B39" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>131934897</v>
       </c>
       <c r="B40" t="n">
-        <v>92544</v>
+        <v>92547</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>131934911</v>
       </c>
       <c r="B41" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>131934932</v>
       </c>
       <c r="B42" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4904,49 +4904,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131934938</v>
+        <v>131934961</v>
       </c>
       <c r="B44" t="n">
-        <v>58107</v>
+        <v>92352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>633911</v>
+        <v>633947</v>
       </c>
       <c r="R44" t="n">
-        <v>6660119</v>
+        <v>6659985</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4978,7 +4974,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4988,12 +4984,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Sång 2st</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5020,45 +5011,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131934961</v>
+        <v>131934938</v>
       </c>
       <c r="B45" t="n">
-        <v>92349</v>
+        <v>58109</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>633947</v>
+        <v>633911</v>
       </c>
       <c r="R45" t="n">
-        <v>6659985</v>
+        <v>6660119</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5090,7 +5085,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5100,7 +5095,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Sång 2st</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5130,7 +5130,7 @@
         <v>131934942</v>
       </c>
       <c r="B46" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>131934894</v>
       </c>
       <c r="B47" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>131934913</v>
       </c>
       <c r="B48" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5475,45 +5475,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131934945</v>
+        <v>131934893</v>
       </c>
       <c r="B49" t="n">
-        <v>79315</v>
+        <v>99098</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>633921</v>
+        <v>634109</v>
       </c>
       <c r="R49" t="n">
-        <v>6660124</v>
+        <v>6659941</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5545,7 +5554,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5555,7 +5564,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5582,54 +5591,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131934893</v>
+        <v>131934945</v>
       </c>
       <c r="B50" t="n">
-        <v>99095</v>
+        <v>79317</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>634109</v>
+        <v>633921</v>
       </c>
       <c r="R50" t="n">
-        <v>6659941</v>
+        <v>6660124</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5701,7 +5701,7 @@
         <v>131934909</v>
       </c>
       <c r="B51" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>131934918</v>
       </c>
       <c r="B52" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>131934889</v>
       </c>
       <c r="B53" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>131934947</v>
       </c>
       <c r="B54" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>131934891</v>
       </c>
       <c r="B55" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>131934912</v>
       </c>
       <c r="B56" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>131934949</v>
       </c>
       <c r="B57" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>131934907</v>
       </c>
       <c r="B58" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6608,32 +6608,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131934931</v>
+        <v>131934946</v>
       </c>
       <c r="B59" t="n">
-        <v>5199</v>
+        <v>79317</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6643,13 +6643,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>633917</v>
+        <v>633930</v>
       </c>
       <c r="R59" t="n">
-        <v>6660062</v>
+        <v>6660120</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6718,7 +6718,7 @@
         <v>131934910</v>
       </c>
       <c r="B60" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6831,32 +6831,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131934946</v>
+        <v>131934931</v>
       </c>
       <c r="B61" t="n">
-        <v>79315</v>
+        <v>5199</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6866,13 +6866,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>633930</v>
+        <v>633917</v>
       </c>
       <c r="R61" t="n">
-        <v>6660120</v>
+        <v>6660062</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6941,7 +6941,7 @@
         <v>131934941</v>
       </c>
       <c r="B62" t="n">
-        <v>92313</v>
+        <v>92316</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>131934915</v>
       </c>
       <c r="B63" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7161,54 +7161,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131934943</v>
+        <v>131934953</v>
       </c>
       <c r="B64" t="n">
-        <v>99095</v>
+        <v>58109</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>633915</v>
+        <v>633814</v>
       </c>
       <c r="R64" t="n">
-        <v>6660086</v>
+        <v>6660115</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -7240,7 +7235,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7250,7 +7245,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7277,49 +7277,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131934953</v>
+        <v>131934943</v>
       </c>
       <c r="B65" t="n">
-        <v>58107</v>
+        <v>99098</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>633814</v>
+        <v>633915</v>
       </c>
       <c r="R65" t="n">
-        <v>6660115</v>
+        <v>6660086</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7351,7 +7356,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7361,12 +7366,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7396,7 +7396,7 @@
         <v>131934963</v>
       </c>
       <c r="B66" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>131934960</v>
       </c>
       <c r="B67" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -4904,10 +4904,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131934961</v>
+        <v>131934942</v>
       </c>
       <c r="B44" t="n">
-        <v>92352</v>
+        <v>99098</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4915,34 +4915,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>633947</v>
+        <v>633913</v>
       </c>
       <c r="R44" t="n">
-        <v>6659985</v>
+        <v>6660082</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4974,7 +4983,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4984,7 +4993,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5011,49 +5020,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131934938</v>
+        <v>131934961</v>
       </c>
       <c r="B45" t="n">
-        <v>58109</v>
+        <v>92352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>633911</v>
+        <v>633947</v>
       </c>
       <c r="R45" t="n">
-        <v>6660119</v>
+        <v>6659985</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5085,7 +5090,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5095,12 +5100,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Sång 2st</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5127,42 +5127,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131934942</v>
+        <v>131934938</v>
       </c>
       <c r="B46" t="n">
-        <v>99098</v>
+        <v>58109</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5171,10 +5166,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>633913</v>
+        <v>633911</v>
       </c>
       <c r="R46" t="n">
-        <v>6660082</v>
+        <v>6660119</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5206,7 +5201,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5216,7 +5211,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Sång 2st</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6715,57 +6715,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131934910</v>
+        <v>131934931</v>
       </c>
       <c r="B60" t="n">
-        <v>99098</v>
+        <v>5199</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>634020</v>
+        <v>633917</v>
       </c>
       <c r="R60" t="n">
-        <v>6660000</v>
+        <v>6660062</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6794,7 +6785,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6804,7 +6795,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6831,48 +6822,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131934931</v>
+        <v>131934910</v>
       </c>
       <c r="B61" t="n">
-        <v>5199</v>
+        <v>99098</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>633917</v>
+        <v>634020</v>
       </c>
       <c r="R61" t="n">
-        <v>6660062</v>
+        <v>6660000</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -4904,10 +4904,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131934942</v>
+        <v>131934961</v>
       </c>
       <c r="B44" t="n">
-        <v>99098</v>
+        <v>92352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4915,43 +4915,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>633913</v>
+        <v>633947</v>
       </c>
       <c r="R44" t="n">
-        <v>6660082</v>
+        <v>6659985</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4983,7 +4974,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4993,7 +4984,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5020,45 +5011,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131934961</v>
+        <v>131934938</v>
       </c>
       <c r="B45" t="n">
-        <v>92352</v>
+        <v>58109</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>633947</v>
+        <v>633911</v>
       </c>
       <c r="R45" t="n">
-        <v>6659985</v>
+        <v>6660119</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5090,7 +5085,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5100,7 +5095,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Sång 2st</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5127,37 +5127,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131934938</v>
+        <v>131934942</v>
       </c>
       <c r="B46" t="n">
-        <v>58109</v>
+        <v>99098</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5166,10 +5171,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>633911</v>
+        <v>633913</v>
       </c>
       <c r="R46" t="n">
-        <v>6660119</v>
+        <v>6660082</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5201,7 +5206,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5211,12 +5216,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Sång 2st</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -4230,54 +4230,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131934895</v>
+        <v>131934964</v>
       </c>
       <c r="B38" t="n">
-        <v>80326</v>
+        <v>91892</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>634086</v>
+        <v>634033</v>
       </c>
       <c r="R38" t="n">
-        <v>6660021</v>
+        <v>6659947</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4309,7 +4300,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4319,7 +4310,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4346,45 +4337,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131934964</v>
+        <v>131934895</v>
       </c>
       <c r="B39" t="n">
-        <v>91892</v>
+        <v>80326</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>634033</v>
+        <v>634086</v>
       </c>
       <c r="R39" t="n">
-        <v>6659947</v>
+        <v>6660021</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4904,10 +4904,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131934961</v>
+        <v>131934942</v>
       </c>
       <c r="B44" t="n">
-        <v>92352</v>
+        <v>99098</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4915,34 +4915,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>633947</v>
+        <v>633913</v>
       </c>
       <c r="R44" t="n">
-        <v>6659985</v>
+        <v>6660082</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4974,7 +4983,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4984,7 +4993,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5011,49 +5020,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131934938</v>
+        <v>131934961</v>
       </c>
       <c r="B45" t="n">
-        <v>58109</v>
+        <v>92352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>633911</v>
+        <v>633947</v>
       </c>
       <c r="R45" t="n">
-        <v>6660119</v>
+        <v>6659985</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5085,7 +5090,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5095,12 +5100,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Sång 2st</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5127,42 +5127,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131934942</v>
+        <v>131934938</v>
       </c>
       <c r="B46" t="n">
-        <v>99098</v>
+        <v>58109</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5171,10 +5166,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>633913</v>
+        <v>633911</v>
       </c>
       <c r="R46" t="n">
-        <v>6660082</v>
+        <v>6660119</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5206,7 +5201,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5216,7 +5211,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Sång 2st</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5475,54 +5475,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131934893</v>
+        <v>131934945</v>
       </c>
       <c r="B49" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>634109</v>
+        <v>633921</v>
       </c>
       <c r="R49" t="n">
-        <v>6659941</v>
+        <v>6660124</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5554,7 +5545,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5564,7 +5555,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5591,45 +5582,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131934945</v>
+        <v>131934893</v>
       </c>
       <c r="B50" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>633921</v>
+        <v>634109</v>
       </c>
       <c r="R50" t="n">
-        <v>6660124</v>
+        <v>6659941</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5814,32 +5814,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131934918</v>
+        <v>131934947</v>
       </c>
       <c r="B52" t="n">
-        <v>92352</v>
+        <v>79317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>633956</v>
+        <v>633961</v>
       </c>
       <c r="R52" t="n">
-        <v>6660067</v>
+        <v>6660116</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6037,32 +6037,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131934947</v>
+        <v>131934918</v>
       </c>
       <c r="B54" t="n">
-        <v>79317</v>
+        <v>92352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>633961</v>
+        <v>633956</v>
       </c>
       <c r="R54" t="n">
-        <v>6660116</v>
+        <v>6660067</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -4904,10 +4904,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131934942</v>
+        <v>131934961</v>
       </c>
       <c r="B44" t="n">
-        <v>99098</v>
+        <v>92352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4915,43 +4915,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>633913</v>
+        <v>633947</v>
       </c>
       <c r="R44" t="n">
-        <v>6660082</v>
+        <v>6659985</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4983,7 +4974,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4993,7 +4984,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5020,45 +5011,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131934961</v>
+        <v>131934938</v>
       </c>
       <c r="B45" t="n">
-        <v>92352</v>
+        <v>58109</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>633947</v>
+        <v>633911</v>
       </c>
       <c r="R45" t="n">
-        <v>6659985</v>
+        <v>6660119</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5090,7 +5085,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5100,7 +5095,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Sång 2st</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5127,37 +5127,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131934938</v>
+        <v>131934942</v>
       </c>
       <c r="B46" t="n">
-        <v>58109</v>
+        <v>99098</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5166,10 +5171,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>633911</v>
+        <v>633913</v>
       </c>
       <c r="R46" t="n">
-        <v>6660119</v>
+        <v>6660082</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5201,7 +5206,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5211,12 +5216,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Sång 2st</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6938,45 +6938,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131934941</v>
+        <v>131934915</v>
       </c>
       <c r="B62" t="n">
-        <v>92316</v>
+        <v>99098</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>633913</v>
+        <v>633972</v>
       </c>
       <c r="R62" t="n">
-        <v>6660092</v>
+        <v>6660005</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -7008,7 +7017,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7018,7 +7027,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7045,54 +7054,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131934915</v>
+        <v>131934941</v>
       </c>
       <c r="B63" t="n">
-        <v>99098</v>
+        <v>92316</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>633972</v>
+        <v>633913</v>
       </c>
       <c r="R63" t="n">
-        <v>6660005</v>
+        <v>6660092</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -4904,10 +4904,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131934961</v>
+        <v>131934942</v>
       </c>
       <c r="B44" t="n">
-        <v>92352</v>
+        <v>99098</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4915,34 +4915,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>633947</v>
+        <v>633913</v>
       </c>
       <c r="R44" t="n">
-        <v>6659985</v>
+        <v>6660082</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4974,7 +4983,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4984,7 +4993,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5011,49 +5020,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131934938</v>
+        <v>131934961</v>
       </c>
       <c r="B45" t="n">
-        <v>58109</v>
+        <v>92352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>633911</v>
+        <v>633947</v>
       </c>
       <c r="R45" t="n">
-        <v>6660119</v>
+        <v>6659985</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5085,7 +5090,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5095,12 +5100,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Sång 2st</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5127,42 +5127,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131934942</v>
+        <v>131934938</v>
       </c>
       <c r="B46" t="n">
-        <v>99098</v>
+        <v>58109</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5171,10 +5166,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>633913</v>
+        <v>633911</v>
       </c>
       <c r="R46" t="n">
-        <v>6660082</v>
+        <v>6660119</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5206,7 +5201,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5216,7 +5211,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Sång 2st</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6938,54 +6938,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131934915</v>
+        <v>131934941</v>
       </c>
       <c r="B62" t="n">
-        <v>99098</v>
+        <v>92316</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>633972</v>
+        <v>633913</v>
       </c>
       <c r="R62" t="n">
-        <v>6660005</v>
+        <v>6660092</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -7017,7 +7008,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7027,7 +7018,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7054,45 +7045,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131934941</v>
+        <v>131934915</v>
       </c>
       <c r="B63" t="n">
-        <v>92316</v>
+        <v>99098</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>633913</v>
+        <v>633972</v>
       </c>
       <c r="R63" t="n">
-        <v>6660092</v>
+        <v>6660005</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -4337,42 +4337,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131934895</v>
+        <v>131934911</v>
       </c>
       <c r="B39" t="n">
-        <v>80326</v>
+        <v>99098</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4381,10 +4381,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>634086</v>
+        <v>634020</v>
       </c>
       <c r="R39" t="n">
-        <v>6660021</v>
+        <v>6659998</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4453,10 +4453,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131934897</v>
+        <v>131934895</v>
       </c>
       <c r="B40" t="n">
-        <v>92547</v>
+        <v>80326</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4464,34 +4464,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1339</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>634103</v>
+        <v>634086</v>
       </c>
       <c r="R40" t="n">
-        <v>6660016</v>
+        <v>6660021</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4523,7 +4532,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4533,7 +4542,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4560,54 +4569,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131934911</v>
+        <v>131934897</v>
       </c>
       <c r="B41" t="n">
-        <v>99098</v>
+        <v>92547</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>634020</v>
+        <v>634103</v>
       </c>
       <c r="R41" t="n">
-        <v>6659998</v>
+        <v>6660016</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4904,10 +4904,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131934942</v>
+        <v>131934961</v>
       </c>
       <c r="B44" t="n">
-        <v>99098</v>
+        <v>92352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4915,43 +4915,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>633913</v>
+        <v>633947</v>
       </c>
       <c r="R44" t="n">
-        <v>6660082</v>
+        <v>6659985</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4983,7 +4974,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4993,7 +4984,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5020,45 +5011,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131934961</v>
+        <v>131934938</v>
       </c>
       <c r="B45" t="n">
-        <v>92352</v>
+        <v>58109</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>633947</v>
+        <v>633911</v>
       </c>
       <c r="R45" t="n">
-        <v>6659985</v>
+        <v>6660119</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5090,7 +5085,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5100,7 +5095,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Sång 2st</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5127,37 +5127,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131934938</v>
+        <v>131934942</v>
       </c>
       <c r="B46" t="n">
-        <v>58109</v>
+        <v>99098</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5166,10 +5171,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>633911</v>
+        <v>633913</v>
       </c>
       <c r="R46" t="n">
-        <v>6660119</v>
+        <v>6660082</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5201,7 +5206,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5211,12 +5216,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Sång 2st</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5921,10 +5921,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131934889</v>
+        <v>131934918</v>
       </c>
       <c r="B53" t="n">
-        <v>99098</v>
+        <v>92352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5932,43 +5932,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>634160</v>
+        <v>633956</v>
       </c>
       <c r="R53" t="n">
-        <v>6659908</v>
+        <v>6660067</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6000,7 +5991,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6010,7 +6001,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6037,10 +6028,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131934918</v>
+        <v>131934889</v>
       </c>
       <c r="B54" t="n">
-        <v>92352</v>
+        <v>99098</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6048,34 +6039,43 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>633956</v>
+        <v>634160</v>
       </c>
       <c r="R54" t="n">
-        <v>6660067</v>
+        <v>6659908</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6608,48 +6608,57 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131934946</v>
+        <v>131934910</v>
       </c>
       <c r="B59" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>633930</v>
+        <v>634020</v>
       </c>
       <c r="R59" t="n">
-        <v>6660120</v>
+        <v>6660000</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6678,7 +6687,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6688,7 +6697,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6715,32 +6724,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131934931</v>
+        <v>131934946</v>
       </c>
       <c r="B60" t="n">
-        <v>5199</v>
+        <v>79317</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6750,13 +6759,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>633917</v>
+        <v>633930</v>
       </c>
       <c r="R60" t="n">
-        <v>6660062</v>
+        <v>6660120</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6785,7 +6794,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6795,7 +6804,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6822,57 +6831,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131934910</v>
+        <v>131934931</v>
       </c>
       <c r="B61" t="n">
-        <v>99098</v>
+        <v>5199</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>634020</v>
+        <v>633917</v>
       </c>
       <c r="R61" t="n">
-        <v>6660000</v>
+        <v>6660062</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -4126,7 +4126,7 @@
         <v>131934890</v>
       </c>
       <c r="B37" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4230,32 +4230,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131934964</v>
+        <v>131934897</v>
       </c>
       <c r="B38" t="n">
-        <v>91892</v>
+        <v>92553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>634033</v>
+        <v>634103</v>
       </c>
       <c r="R38" t="n">
-        <v>6659947</v>
+        <v>6660016</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4337,54 +4337,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131934911</v>
+        <v>131934964</v>
       </c>
       <c r="B39" t="n">
-        <v>99098</v>
+        <v>91898</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>634020</v>
+        <v>634033</v>
       </c>
       <c r="R39" t="n">
-        <v>6659998</v>
+        <v>6659947</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4416,7 +4407,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4426,7 +4417,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4453,42 +4444,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131934895</v>
+        <v>131934911</v>
       </c>
       <c r="B40" t="n">
-        <v>80326</v>
+        <v>99106</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4497,10 +4488,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>634086</v>
+        <v>634020</v>
       </c>
       <c r="R40" t="n">
-        <v>6660021</v>
+        <v>6659998</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4532,7 +4523,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4542,7 +4533,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4569,10 +4560,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131934897</v>
+        <v>131934895</v>
       </c>
       <c r="B41" t="n">
-        <v>92547</v>
+        <v>80328</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4580,34 +4571,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1339</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>634103</v>
+        <v>634086</v>
       </c>
       <c r="R41" t="n">
-        <v>6660016</v>
+        <v>6660021</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4679,7 +4679,7 @@
         <v>131934932</v>
       </c>
       <c r="B42" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>131934914</v>
       </c>
       <c r="B43" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131934961</v>
+        <v>131934942</v>
       </c>
       <c r="B44" t="n">
-        <v>92352</v>
+        <v>99106</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4915,34 +4915,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>633947</v>
+        <v>633913</v>
       </c>
       <c r="R44" t="n">
-        <v>6659985</v>
+        <v>6660082</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4974,7 +4983,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4984,7 +4993,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5011,49 +5020,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131934938</v>
+        <v>131934961</v>
       </c>
       <c r="B45" t="n">
-        <v>58109</v>
+        <v>92358</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>633911</v>
+        <v>633947</v>
       </c>
       <c r="R45" t="n">
-        <v>6660119</v>
+        <v>6659985</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5085,7 +5090,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5095,12 +5100,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Sång 2st</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5127,42 +5127,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131934942</v>
+        <v>131934938</v>
       </c>
       <c r="B46" t="n">
-        <v>99098</v>
+        <v>58110</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5171,10 +5166,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>633913</v>
+        <v>633911</v>
       </c>
       <c r="R46" t="n">
-        <v>6660082</v>
+        <v>6660119</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5206,7 +5201,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5216,7 +5211,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Sång 2st</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5246,7 +5246,7 @@
         <v>131934894</v>
       </c>
       <c r="B47" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>131934913</v>
       </c>
       <c r="B48" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>131934945</v>
       </c>
       <c r="B49" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>131934893</v>
       </c>
       <c r="B50" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>131934909</v>
       </c>
       <c r="B51" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>131934947</v>
       </c>
       <c r="B52" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>131934918</v>
       </c>
       <c r="B53" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>131934889</v>
       </c>
       <c r="B54" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>131934891</v>
       </c>
       <c r="B55" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6260,10 +6260,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131934912</v>
+        <v>131934949</v>
       </c>
       <c r="B56" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>634027</v>
+        <v>633932</v>
       </c>
       <c r="R56" t="n">
-        <v>6659983</v>
+        <v>6660096</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6376,10 +6376,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131934949</v>
+        <v>131934912</v>
       </c>
       <c r="B57" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>633932</v>
+        <v>634027</v>
       </c>
       <c r="R57" t="n">
-        <v>6660096</v>
+        <v>6659983</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6495,7 +6495,7 @@
         <v>131934907</v>
       </c>
       <c r="B58" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6608,57 +6608,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131934910</v>
+        <v>131934931</v>
       </c>
       <c r="B59" t="n">
-        <v>99098</v>
+        <v>5199</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>634020</v>
+        <v>633917</v>
       </c>
       <c r="R59" t="n">
-        <v>6660000</v>
+        <v>6660062</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6687,7 +6678,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6697,7 +6688,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6724,48 +6715,57 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131934946</v>
+        <v>131934910</v>
       </c>
       <c r="B60" t="n">
-        <v>79317</v>
+        <v>99106</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>633930</v>
+        <v>634020</v>
       </c>
       <c r="R60" t="n">
-        <v>6660120</v>
+        <v>6660000</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6831,32 +6831,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131934931</v>
+        <v>131934946</v>
       </c>
       <c r="B61" t="n">
-        <v>5199</v>
+        <v>79319</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6866,13 +6866,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>633917</v>
+        <v>633930</v>
       </c>
       <c r="R61" t="n">
-        <v>6660062</v>
+        <v>6660120</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6938,45 +6938,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131934941</v>
+        <v>131934915</v>
       </c>
       <c r="B62" t="n">
-        <v>92316</v>
+        <v>99106</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>633913</v>
+        <v>633972</v>
       </c>
       <c r="R62" t="n">
-        <v>6660092</v>
+        <v>6660005</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -7008,7 +7017,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7018,7 +7027,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7045,54 +7054,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131934915</v>
+        <v>131934941</v>
       </c>
       <c r="B63" t="n">
-        <v>99098</v>
+        <v>92322</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>633972</v>
+        <v>633913</v>
       </c>
       <c r="R63" t="n">
-        <v>6660005</v>
+        <v>6660092</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7164,7 +7164,7 @@
         <v>131934953</v>
       </c>
       <c r="B64" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>131934943</v>
       </c>
       <c r="B65" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>131934963</v>
       </c>
       <c r="B66" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>131934960</v>
       </c>
       <c r="B67" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -5020,45 +5020,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131934961</v>
+        <v>131934938</v>
       </c>
       <c r="B45" t="n">
-        <v>92358</v>
+        <v>58110</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>633947</v>
+        <v>633911</v>
       </c>
       <c r="R45" t="n">
-        <v>6659985</v>
+        <v>6660119</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5090,7 +5094,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5100,7 +5104,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Sång 2st</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5127,49 +5136,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131934938</v>
+        <v>131934961</v>
       </c>
       <c r="B46" t="n">
-        <v>58110</v>
+        <v>92358</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>633911</v>
+        <v>633947</v>
       </c>
       <c r="R46" t="n">
-        <v>6660119</v>
+        <v>6659985</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5201,7 +5206,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5211,12 +5216,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Sång 2st</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5814,45 +5814,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131934947</v>
+        <v>131934889</v>
       </c>
       <c r="B52" t="n">
-        <v>79319</v>
+        <v>99106</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>633961</v>
+        <v>634160</v>
       </c>
       <c r="R52" t="n">
-        <v>6660116</v>
+        <v>6659908</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -5884,7 +5893,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5894,7 +5903,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5921,32 +5930,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131934918</v>
+        <v>131934947</v>
       </c>
       <c r="B53" t="n">
-        <v>92358</v>
+        <v>79319</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5956,10 +5965,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>633956</v>
+        <v>633961</v>
       </c>
       <c r="R53" t="n">
-        <v>6660067</v>
+        <v>6660116</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5991,7 +6000,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6001,7 +6010,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6028,10 +6037,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131934889</v>
+        <v>131934918</v>
       </c>
       <c r="B54" t="n">
-        <v>99106</v>
+        <v>92358</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6039,43 +6048,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>634160</v>
+        <v>633956</v>
       </c>
       <c r="R54" t="n">
-        <v>6659908</v>
+        <v>6660067</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7161,49 +7161,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131934953</v>
+        <v>131934943</v>
       </c>
       <c r="B64" t="n">
-        <v>58110</v>
+        <v>99106</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>633814</v>
+        <v>633915</v>
       </c>
       <c r="R64" t="n">
-        <v>6660115</v>
+        <v>6660086</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -7235,7 +7240,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7245,12 +7250,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7277,54 +7277,49 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131934943</v>
+        <v>131934953</v>
       </c>
       <c r="B65" t="n">
-        <v>99106</v>
+        <v>58110</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>633915</v>
+        <v>633814</v>
       </c>
       <c r="R65" t="n">
-        <v>6660086</v>
+        <v>6660115</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7356,7 +7351,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7366,7 +7361,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -4126,7 +4126,7 @@
         <v>131934890</v>
       </c>
       <c r="B37" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4230,10 +4230,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131934897</v>
+        <v>131934895</v>
       </c>
       <c r="B38" t="n">
-        <v>92553</v>
+        <v>80336</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4241,34 +4241,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1339</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>634103</v>
+        <v>634086</v>
       </c>
       <c r="R38" t="n">
-        <v>6660016</v>
+        <v>6660021</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4300,7 +4309,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4310,7 +4319,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4340,7 +4349,7 @@
         <v>131934964</v>
       </c>
       <c r="B39" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4444,54 +4453,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131934911</v>
+        <v>131934897</v>
       </c>
       <c r="B40" t="n">
-        <v>99106</v>
+        <v>92563</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>634020</v>
+        <v>634103</v>
       </c>
       <c r="R40" t="n">
-        <v>6659998</v>
+        <v>6660016</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4560,42 +4560,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131934895</v>
+        <v>131934911</v>
       </c>
       <c r="B41" t="n">
-        <v>80328</v>
+        <v>99116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>634086</v>
+        <v>634020</v>
       </c>
       <c r="R41" t="n">
-        <v>6660021</v>
+        <v>6659998</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4679,7 +4679,7 @@
         <v>131934932</v>
       </c>
       <c r="B42" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>131934914</v>
       </c>
       <c r="B43" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131934942</v>
+        <v>131934961</v>
       </c>
       <c r="B44" t="n">
-        <v>99106</v>
+        <v>92368</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4915,43 +4915,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>633913</v>
+        <v>633947</v>
       </c>
       <c r="R44" t="n">
-        <v>6660082</v>
+        <v>6659985</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4983,7 +4974,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4993,7 +4984,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5023,7 +5014,7 @@
         <v>131934938</v>
       </c>
       <c r="B45" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5136,10 +5127,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131934961</v>
+        <v>131934942</v>
       </c>
       <c r="B46" t="n">
-        <v>92358</v>
+        <v>99116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5147,34 +5138,43 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>633947</v>
+        <v>633913</v>
       </c>
       <c r="R46" t="n">
-        <v>6659985</v>
+        <v>6660082</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5246,7 +5246,7 @@
         <v>131934894</v>
       </c>
       <c r="B47" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>131934913</v>
       </c>
       <c r="B48" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5475,45 +5475,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131934945</v>
+        <v>131934893</v>
       </c>
       <c r="B49" t="n">
-        <v>79319</v>
+        <v>99116</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>633921</v>
+        <v>634109</v>
       </c>
       <c r="R49" t="n">
-        <v>6660124</v>
+        <v>6659941</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5545,7 +5554,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5555,7 +5564,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5582,54 +5591,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131934893</v>
+        <v>131934945</v>
       </c>
       <c r="B50" t="n">
-        <v>99106</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>634109</v>
+        <v>633921</v>
       </c>
       <c r="R50" t="n">
-        <v>6659941</v>
+        <v>6660124</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5701,7 +5701,7 @@
         <v>131934909</v>
       </c>
       <c r="B51" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5814,10 +5814,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131934889</v>
+        <v>131934918</v>
       </c>
       <c r="B52" t="n">
-        <v>99106</v>
+        <v>92368</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5825,43 +5825,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>634160</v>
+        <v>633956</v>
       </c>
       <c r="R52" t="n">
-        <v>6659908</v>
+        <v>6660067</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -5893,7 +5884,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5903,7 +5894,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5933,7 +5924,7 @@
         <v>131934947</v>
       </c>
       <c r="B53" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6037,10 +6028,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131934918</v>
+        <v>131934889</v>
       </c>
       <c r="B54" t="n">
-        <v>92358</v>
+        <v>99116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6048,34 +6039,43 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>633956</v>
+        <v>634160</v>
       </c>
       <c r="R54" t="n">
-        <v>6660067</v>
+        <v>6659908</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6147,7 +6147,7 @@
         <v>131934891</v>
       </c>
       <c r="B55" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6260,10 +6260,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131934949</v>
+        <v>131934912</v>
       </c>
       <c r="B56" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>633932</v>
+        <v>634027</v>
       </c>
       <c r="R56" t="n">
-        <v>6660096</v>
+        <v>6659983</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6376,10 +6376,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131934912</v>
+        <v>131934949</v>
       </c>
       <c r="B57" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>634027</v>
+        <v>633932</v>
       </c>
       <c r="R57" t="n">
-        <v>6659983</v>
+        <v>6660096</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6495,7 +6495,7 @@
         <v>131934907</v>
       </c>
       <c r="B58" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6608,32 +6608,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131934931</v>
+        <v>131934946</v>
       </c>
       <c r="B59" t="n">
-        <v>5199</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6643,13 +6643,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>633917</v>
+        <v>633930</v>
       </c>
       <c r="R59" t="n">
-        <v>6660062</v>
+        <v>6660120</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6715,57 +6715,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131934910</v>
+        <v>131934931</v>
       </c>
       <c r="B60" t="n">
-        <v>99106</v>
+        <v>5199</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>634020</v>
+        <v>633917</v>
       </c>
       <c r="R60" t="n">
-        <v>6660000</v>
+        <v>6660062</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6794,7 +6785,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6804,7 +6795,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6831,48 +6822,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131934946</v>
+        <v>131934910</v>
       </c>
       <c r="B61" t="n">
-        <v>79319</v>
+        <v>99116</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>633930</v>
+        <v>634020</v>
       </c>
       <c r="R61" t="n">
-        <v>6660120</v>
+        <v>6660000</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6938,54 +6938,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131934915</v>
+        <v>131934941</v>
       </c>
       <c r="B62" t="n">
-        <v>99106</v>
+        <v>92332</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>633972</v>
+        <v>633913</v>
       </c>
       <c r="R62" t="n">
-        <v>6660005</v>
+        <v>6660092</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -7017,7 +7008,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7027,7 +7018,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7054,45 +7045,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131934941</v>
+        <v>131934915</v>
       </c>
       <c r="B63" t="n">
-        <v>92322</v>
+        <v>99116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>633913</v>
+        <v>633972</v>
       </c>
       <c r="R63" t="n">
-        <v>6660092</v>
+        <v>6660005</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7161,54 +7161,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131934943</v>
+        <v>131934953</v>
       </c>
       <c r="B64" t="n">
-        <v>99106</v>
+        <v>58114</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>633915</v>
+        <v>633814</v>
       </c>
       <c r="R64" t="n">
-        <v>6660086</v>
+        <v>6660115</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -7240,7 +7235,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7250,7 +7245,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7277,49 +7277,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131934953</v>
+        <v>131934943</v>
       </c>
       <c r="B65" t="n">
-        <v>58110</v>
+        <v>99116</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>633814</v>
+        <v>633915</v>
       </c>
       <c r="R65" t="n">
-        <v>6660115</v>
+        <v>6660086</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7351,7 +7356,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7361,12 +7366,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7396,7 +7396,7 @@
         <v>131934963</v>
       </c>
       <c r="B66" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>131934960</v>
       </c>
       <c r="B67" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -6608,48 +6608,57 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131934946</v>
+        <v>131934910</v>
       </c>
       <c r="B59" t="n">
-        <v>79327</v>
+        <v>99116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>633930</v>
+        <v>634020</v>
       </c>
       <c r="R59" t="n">
-        <v>6660120</v>
+        <v>6660000</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6678,7 +6687,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6688,7 +6697,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6715,32 +6724,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131934931</v>
+        <v>131934946</v>
       </c>
       <c r="B60" t="n">
-        <v>5199</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6750,13 +6759,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>633917</v>
+        <v>633930</v>
       </c>
       <c r="R60" t="n">
-        <v>6660062</v>
+        <v>6660120</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6785,7 +6794,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6795,7 +6804,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6822,57 +6831,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131934910</v>
+        <v>131934931</v>
       </c>
       <c r="B61" t="n">
-        <v>99116</v>
+        <v>5199</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>634020</v>
+        <v>633917</v>
       </c>
       <c r="R61" t="n">
-        <v>6660000</v>
+        <v>6660062</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38085-2025 artfynd.xlsx
+++ b/artfynd/A 38085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127822938</v>
+        <v>127822928</v>
       </c>
       <c r="B2" t="n">
-        <v>95904</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2666</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634244</v>
+        <v>633845</v>
       </c>
       <c r="R2" t="n">
-        <v>6660097</v>
+        <v>6660107</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127822935</v>
+        <v>127822929</v>
       </c>
       <c r="B3" t="n">
-        <v>80406</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228430</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633889</v>
+        <v>633826</v>
       </c>
       <c r="R3" t="n">
-        <v>6660133</v>
+        <v>6660104</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127822929</v>
+        <v>127822930</v>
       </c>
       <c r="B4" t="n">
-        <v>96823</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633826</v>
+        <v>633823</v>
       </c>
       <c r="R4" t="n">
-        <v>6660104</v>
+        <v>6660105</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127822932</v>
+        <v>127822931</v>
       </c>
       <c r="B5" t="n">
-        <v>91417</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633825</v>
+        <v>633818</v>
       </c>
       <c r="R5" t="n">
-        <v>6660111</v>
+        <v>6660122</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127822940</v>
+        <v>129963906</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633924</v>
+        <v>634204</v>
       </c>
       <c r="R6" t="n">
-        <v>6660133</v>
+        <v>6659818</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127822939</v>
+        <v>129963909</v>
       </c>
       <c r="B7" t="n">
-        <v>4779</v>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633892</v>
+        <v>633861</v>
       </c>
       <c r="R7" t="n">
-        <v>6660109</v>
+        <v>6660092</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127822933</v>
+        <v>129963910</v>
       </c>
       <c r="B8" t="n">
-        <v>90954</v>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>256703</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633944</v>
+        <v>634095</v>
       </c>
       <c r="R8" t="n">
-        <v>6660092</v>
+        <v>6659891</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1354,45 +1354,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127822926</v>
+        <v>127822927</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>91375</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>720</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633792</v>
+        <v>633787</v>
       </c>
       <c r="R9" t="n">
-        <v>6660101</v>
+        <v>6660108</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1433,6 +1444,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1451,10 +1463,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127822927</v>
+        <v>127847536</v>
       </c>
       <c r="B10" t="n">
-        <v>90927</v>
+        <v>92605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,45 +1474,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>720</v>
+        <v>898</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633787</v>
+        <v>634214</v>
       </c>
       <c r="R10" t="n">
-        <v>6660108</v>
+        <v>6659848</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1527,12 +1528,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1541,7 +1542,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1560,10 +1560,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127822930</v>
+        <v>127847513</v>
       </c>
       <c r="B11" t="n">
-        <v>96823</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633823</v>
+        <v>634214</v>
       </c>
       <c r="R11" t="n">
-        <v>6660105</v>
+        <v>6659847</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1657,10 +1657,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127822928</v>
+        <v>131934935</v>
       </c>
       <c r="B12" t="n">
-        <v>96823</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,37 +1668,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633845</v>
+        <v>633904</v>
       </c>
       <c r="R12" t="n">
-        <v>6660107</v>
+        <v>6660025</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1722,12 +1722,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1754,48 +1764,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127822936</v>
+        <v>131934940</v>
       </c>
       <c r="B13" t="n">
-        <v>95902</v>
+        <v>91974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2667</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>634236</v>
+        <v>633887</v>
       </c>
       <c r="R13" t="n">
-        <v>6660081</v>
+        <v>6660093</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1819,12 +1829,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1851,10 +1871,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127822931</v>
+        <v>131934962</v>
       </c>
       <c r="B14" t="n">
-        <v>96823</v>
+        <v>91974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1862,37 +1882,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633818</v>
+        <v>633994</v>
       </c>
       <c r="R14" t="n">
-        <v>6660122</v>
+        <v>6659971</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1916,12 +1936,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1948,48 +1978,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127847537</v>
+        <v>131934964</v>
       </c>
       <c r="B15" t="n">
-        <v>8439</v>
+        <v>91974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>634222</v>
+        <v>634033</v>
       </c>
       <c r="R15" t="n">
-        <v>6659810</v>
+        <v>6659947</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2013,12 +2043,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2045,45 +2085,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127847524</v>
+        <v>127847511</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634229</v>
+        <v>634202</v>
       </c>
       <c r="R16" t="n">
-        <v>6659801</v>
+        <v>6659850</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2118,12 +2161,18 @@
           <t>2025-08-26</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Intorkad på liggande gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2142,14 +2191,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127847511</v>
+        <v>129963922</v>
       </c>
       <c r="B17" t="n">
-        <v>91918</v>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2162,31 +2211,28 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634202</v>
+        <v>634101</v>
       </c>
       <c r="R17" t="n">
-        <v>6659850</v>
+        <v>6659953</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2210,17 +2256,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Intorkad på liggande gran</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2229,7 +2270,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2248,48 +2288,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127847536</v>
+        <v>131934890</v>
       </c>
       <c r="B18" t="n">
-        <v>92134</v>
+        <v>92406</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>634214</v>
+        <v>634105</v>
       </c>
       <c r="R18" t="n">
-        <v>6659848</v>
+        <v>6659941</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2313,12 +2353,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2345,48 +2395,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127847540</v>
+        <v>131934918</v>
       </c>
       <c r="B19" t="n">
-        <v>91517</v>
+        <v>92406</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5321</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>634239</v>
+        <v>633956</v>
       </c>
       <c r="R19" t="n">
-        <v>6659810</v>
+        <v>6660067</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2410,12 +2460,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2424,7 +2484,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2443,48 +2502,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127847519</v>
+        <v>131934960</v>
       </c>
       <c r="B20" t="n">
-        <v>95914</v>
+        <v>92406</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2667</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>634194</v>
+        <v>633946</v>
       </c>
       <c r="R20" t="n">
-        <v>6659965</v>
+        <v>6660010</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2508,12 +2567,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2540,48 +2609,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127847526</v>
+        <v>131934961</v>
       </c>
       <c r="B21" t="n">
-        <v>98585</v>
+        <v>92406</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>634229</v>
+        <v>633947</v>
       </c>
       <c r="R21" t="n">
-        <v>6659844</v>
+        <v>6659985</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2605,12 +2674,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2637,48 +2716,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127847522</v>
+        <v>131934963</v>
       </c>
       <c r="B22" t="n">
-        <v>98585</v>
+        <v>92406</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>634236</v>
+        <v>634033</v>
       </c>
       <c r="R22" t="n">
-        <v>6659806</v>
+        <v>6659947</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2702,17 +2781,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>15 bladrosette</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2739,10 +2823,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127847539</v>
+        <v>131934897</v>
       </c>
       <c r="B23" t="n">
-        <v>91517</v>
+        <v>92647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2750,37 +2834,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5321</v>
+        <v>1339</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>634243</v>
+        <v>634103</v>
       </c>
       <c r="R23" t="n">
-        <v>6659820</v>
+        <v>6660016</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2804,12 +2888,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2818,7 +2912,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2837,32 +2930,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127847513</v>
+        <v>127822938</v>
       </c>
       <c r="B24" t="n">
-        <v>91464</v>
+        <v>96439</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2666</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2872,10 +2965,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>634214</v>
+        <v>634244</v>
       </c>
       <c r="R24" t="n">
-        <v>6659847</v>
+        <v>6660097</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2902,12 +2995,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2934,32 +3027,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127847528</v>
+        <v>127822936</v>
       </c>
       <c r="B25" t="n">
-        <v>98585</v>
+        <v>96437</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2969,10 +3062,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>634243</v>
+        <v>634236</v>
       </c>
       <c r="R25" t="n">
-        <v>6659813</v>
+        <v>6660081</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -2999,17 +3092,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>40 bladrosetter</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3036,32 +3124,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129408823</v>
+        <v>127847519</v>
       </c>
       <c r="B26" t="n">
-        <v>98780</v>
+        <v>96437</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3071,13 +3159,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>633912</v>
+        <v>634194</v>
       </c>
       <c r="R26" t="n">
-        <v>6660074</v>
+        <v>6659965</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3101,12 +3189,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3133,48 +3221,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129408822</v>
+        <v>131934956</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>96410</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>634152</v>
+        <v>633786</v>
       </c>
       <c r="R27" t="n">
-        <v>6659919</v>
+        <v>6660096</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3198,12 +3286,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3230,48 +3328,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129408824</v>
+        <v>131934941</v>
       </c>
       <c r="B28" t="n">
-        <v>98780</v>
+        <v>92370</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>634203</v>
+        <v>633913</v>
       </c>
       <c r="R28" t="n">
-        <v>6659855</v>
+        <v>6660092</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3295,12 +3393,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3327,32 +3435,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129963932</v>
+        <v>127847539</v>
       </c>
       <c r="B29" t="n">
-        <v>98920</v>
+        <v>91966</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,13 +3470,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>634159</v>
+        <v>634243</v>
       </c>
       <c r="R29" t="n">
-        <v>6659902</v>
+        <v>6659820</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3392,17 +3500,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3411,6 +3514,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3429,10 +3533,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129963923</v>
+        <v>127847540</v>
       </c>
       <c r="B30" t="n">
-        <v>97791</v>
+        <v>91966</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3440,21 +3544,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>5321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3464,13 +3568,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>634194</v>
+        <v>634239</v>
       </c>
       <c r="R30" t="n">
-        <v>6659850</v>
+        <v>6659810</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3494,12 +3598,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3508,6 +3612,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3526,10 +3631,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129963925</v>
+        <v>127822932</v>
       </c>
       <c r="B31" t="n">
-        <v>97791</v>
+        <v>91872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3537,21 +3642,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3561,13 +3666,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>634068</v>
+        <v>633825</v>
       </c>
       <c r="R31" t="n">
-        <v>6660027</v>
+        <v>6660111</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3591,12 +3696,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3623,32 +3728,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129963931</v>
+        <v>129963911</v>
       </c>
       <c r="B32" t="n">
-        <v>98920</v>
+        <v>91872</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3658,10 +3763,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633898</v>
+        <v>634133</v>
       </c>
       <c r="R32" t="n">
-        <v>6660073</v>
+        <v>6659883</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3694,11 +3799,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>1 bukett</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3725,48 +3825,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129963922</v>
+        <v>131934965</v>
       </c>
       <c r="B33" t="n">
-        <v>92181</v>
+        <v>91937</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>634101</v>
+        <v>634127</v>
       </c>
       <c r="R33" t="n">
-        <v>6659953</v>
+        <v>6659888</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3790,12 +3890,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3822,10 +3932,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129963930</v>
+        <v>127822940</v>
       </c>
       <c r="B34" t="n">
-        <v>98920</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,21 +3943,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,13 +3967,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>634153</v>
+        <v>633924</v>
       </c>
       <c r="R34" t="n">
-        <v>6659918</v>
+        <v>6660133</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3887,17 +3997,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>30 buketter</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3924,10 +4029,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129963929</v>
+        <v>131934945</v>
       </c>
       <c r="B35" t="n">
-        <v>98920</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3935,37 +4040,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>633905</v>
+        <v>633921</v>
       </c>
       <c r="R35" t="n">
-        <v>6660069</v>
+        <v>6660124</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3989,17 +4094,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>7 buketter</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4026,48 +4136,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129963904</v>
+        <v>131934946</v>
       </c>
       <c r="B36" t="n">
-        <v>5197</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>633920</v>
+        <v>633930</v>
       </c>
       <c r="R36" t="n">
-        <v>6660072</v>
+        <v>6660120</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4091,12 +4201,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4123,10 +4243,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131934890</v>
+        <v>131934947</v>
       </c>
       <c r="B37" t="n">
-        <v>92368</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4134,21 +4254,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4158,10 +4278,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>634105</v>
+        <v>633961</v>
       </c>
       <c r="R37" t="n">
-        <v>6659941</v>
+        <v>6660116</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4193,7 +4313,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4203,7 +4323,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4233,7 +4353,7 @@
         <v>131934895</v>
       </c>
       <c r="B38" t="n">
-        <v>80336</v>
+        <v>80382</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4346,32 +4466,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131934964</v>
+        <v>131934914</v>
       </c>
       <c r="B39" t="n">
-        <v>91908</v>
+        <v>57972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4381,13 +4501,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>634033</v>
+        <v>633995</v>
       </c>
       <c r="R39" t="n">
-        <v>6659947</v>
+        <v>6660007</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4416,7 +4536,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4426,7 +4546,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4453,10 +4578,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131934897</v>
+        <v>131934936</v>
       </c>
       <c r="B40" t="n">
-        <v>92563</v>
+        <v>57972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4464,21 +4589,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4488,10 +4613,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>634103</v>
+        <v>633907</v>
       </c>
       <c r="R40" t="n">
-        <v>6660016</v>
+        <v>6660029</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4523,7 +4648,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4533,7 +4658,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4560,57 +4690,52 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131934911</v>
+        <v>129963928</v>
       </c>
       <c r="B41" t="n">
-        <v>99116</v>
+        <v>58067</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100090</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>634020</v>
+        <v>634164</v>
       </c>
       <c r="R41" t="n">
-        <v>6659998</v>
+        <v>6659855</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4634,22 +4759,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hördes vid flera tillfällen</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4676,57 +4796,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131934932</v>
+        <v>127822939</v>
       </c>
       <c r="B42" t="n">
-        <v>99116</v>
+        <v>4781</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>633904</v>
+        <v>633892</v>
       </c>
       <c r="R42" t="n">
-        <v>6660068</v>
+        <v>6660109</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4750,22 +4861,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4792,10 +4893,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131934914</v>
+        <v>131934938</v>
       </c>
       <c r="B43" t="n">
-        <v>57950</v>
+        <v>58136</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4803,37 +4904,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>633995</v>
+        <v>633911</v>
       </c>
       <c r="R43" t="n">
-        <v>6660007</v>
+        <v>6660119</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4862,7 +4967,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4872,12 +4977,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>Sång 2st</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4904,45 +5009,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131934961</v>
+        <v>131934953</v>
       </c>
       <c r="B44" t="n">
-        <v>92368</v>
+        <v>58136</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>633947</v>
+        <v>633814</v>
       </c>
       <c r="R44" t="n">
-        <v>6659985</v>
+        <v>6660115</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4974,7 +5083,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4984,7 +5093,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5011,52 +5125,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131934938</v>
+        <v>127822926</v>
       </c>
       <c r="B45" t="n">
-        <v>58114</v>
+        <v>5199</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>633911</v>
+        <v>633792</v>
       </c>
       <c r="R45" t="n">
-        <v>6660119</v>
+        <v>6660101</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5080,27 +5190,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Sång 2st</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5127,57 +5222,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131934942</v>
+        <v>129963904</v>
       </c>
       <c r="B46" t="n">
-        <v>99116</v>
+        <v>5199</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>633913</v>
+        <v>633920</v>
       </c>
       <c r="R46" t="n">
-        <v>6660082</v>
+        <v>6660072</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5201,22 +5287,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5243,57 +5319,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131934894</v>
+        <v>129963905</v>
       </c>
       <c r="B47" t="n">
-        <v>99116</v>
+        <v>5199</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>634087</v>
+        <v>634134</v>
       </c>
       <c r="R47" t="n">
-        <v>6659966</v>
+        <v>6659887</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5317,22 +5384,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5359,57 +5416,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131934913</v>
+        <v>131934931</v>
       </c>
       <c r="B48" t="n">
-        <v>99116</v>
+        <v>5201</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>634020</v>
+        <v>633917</v>
       </c>
       <c r="R48" t="n">
-        <v>6659988</v>
+        <v>6660062</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5438,7 +5486,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5448,7 +5496,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5475,57 +5523,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131934893</v>
+        <v>127847537</v>
       </c>
       <c r="B49" t="n">
-        <v>99116</v>
+        <v>8444</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>634109</v>
+        <v>634222</v>
       </c>
       <c r="R49" t="n">
-        <v>6659941</v>
+        <v>6659810</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5549,22 +5588,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5591,48 +5620,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131934945</v>
+        <v>127847522</v>
       </c>
       <c r="B50" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>633921</v>
+        <v>634236</v>
       </c>
       <c r="R50" t="n">
-        <v>6660124</v>
+        <v>6659806</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5656,22 +5685,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>15 bladrosette</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5698,10 +5722,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131934909</v>
+        <v>127847524</v>
       </c>
       <c r="B51" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5726,29 +5750,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>634018</v>
+        <v>634229</v>
       </c>
       <c r="R51" t="n">
-        <v>6660002</v>
+        <v>6659801</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5772,22 +5787,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5814,10 +5819,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131934918</v>
+        <v>127847526</v>
       </c>
       <c r="B52" t="n">
-        <v>92368</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5825,37 +5830,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>633956</v>
+        <v>634229</v>
       </c>
       <c r="R52" t="n">
-        <v>6660067</v>
+        <v>6659844</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5879,22 +5884,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:34</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:34</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5921,48 +5916,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131934947</v>
+        <v>127847528</v>
       </c>
       <c r="B53" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>633961</v>
+        <v>634243</v>
       </c>
       <c r="R53" t="n">
-        <v>6660116</v>
+        <v>6659813</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5986,22 +5981,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>40 bladrosetter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6028,10 +6018,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131934889</v>
+        <v>129408822</v>
       </c>
       <c r="B54" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6056,29 +6046,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>634160</v>
+        <v>634152</v>
       </c>
       <c r="R54" t="n">
-        <v>6659908</v>
+        <v>6659919</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6102,22 +6083,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:43</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:43</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6144,10 +6115,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131934891</v>
+        <v>129408823</v>
       </c>
       <c r="B55" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6172,29 +6143,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>634107</v>
+        <v>633912</v>
       </c>
       <c r="R55" t="n">
-        <v>6659939</v>
+        <v>6660074</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6218,22 +6180,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6260,10 +6212,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131934912</v>
+        <v>129408824</v>
       </c>
       <c r="B56" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6288,29 +6240,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>634027</v>
+        <v>634203</v>
       </c>
       <c r="R56" t="n">
-        <v>6659983</v>
+        <v>6659855</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6334,22 +6277,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6376,10 +6309,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131934949</v>
+        <v>129963929</v>
       </c>
       <c r="B57" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6404,29 +6337,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>633932</v>
+        <v>633905</v>
       </c>
       <c r="R57" t="n">
-        <v>6660096</v>
+        <v>6660069</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6450,22 +6374,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>7 buketter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6492,10 +6411,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131934907</v>
+        <v>129963930</v>
       </c>
       <c r="B58" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6520,29 +6439,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>633997</v>
+        <v>634153</v>
       </c>
       <c r="R58" t="n">
-        <v>6660017</v>
+        <v>6659918</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6566,22 +6476,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>30 buketter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6608,10 +6513,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131934910</v>
+        <v>129963931</v>
       </c>
       <c r="B59" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6636,29 +6541,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>634020</v>
+        <v>633898</v>
       </c>
       <c r="R59" t="n">
-        <v>6660000</v>
+        <v>6660073</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6682,22 +6578,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6724,48 +6615,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131934946</v>
+        <v>129963932</v>
       </c>
       <c r="B60" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Enbärsmossarna O, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>633930</v>
+        <v>634159</v>
       </c>
       <c r="R60" t="n">
-        <v>6660120</v>
+        <v>6659902</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6789,22 +6680,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6831,48 +6717,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131934931</v>
+        <v>131934888</v>
       </c>
       <c r="B61" t="n">
-        <v>5199</v>
+        <v>99195</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>633917</v>
+        <v>634234</v>
       </c>
       <c r="R61" t="n">
-        <v>6660062</v>
+        <v>6659794</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6901,7 +6796,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6911,7 +6806,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6938,45 +6833,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131934941</v>
+        <v>131934889</v>
       </c>
       <c r="B62" t="n">
-        <v>92332</v>
+        <v>99195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>633913</v>
+        <v>634160</v>
       </c>
       <c r="R62" t="n">
-        <v>6660092</v>
+        <v>6659908</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -7008,7 +6912,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7018,7 +6922,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7045,10 +6949,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131934915</v>
+        <v>131934891</v>
       </c>
       <c r="B63" t="n">
-        <v>99116</v>
+        <v>99195</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7075,7 +6979,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7089,10 +6993,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>633972</v>
+        <v>634107</v>
       </c>
       <c r="R63" t="n">
-        <v>6660005</v>
+        <v>6659939</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -7124,7 +7028,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7134,7 +7038,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7161,49 +7065,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131934953</v>
+        <v>131934893</v>
       </c>
       <c r="B64" t="n">
-        <v>58114</v>
+        <v>99195</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>633814</v>
+        <v>634109</v>
       </c>
       <c r="R64" t="n">
-        <v>6660115</v>
+        <v>6659941</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -7235,7 +7144,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7245,12 +7154,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7277,10 +7181,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131934943</v>
+        <v>131934894</v>
       </c>
       <c r="B65" t="n">
-        <v>99116</v>
+        <v>99195</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7307,7 +7211,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7321,10 +7225,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>633915</v>
+        <v>634087</v>
       </c>
       <c r="R65" t="n">
-        <v>6660086</v>
+        <v>6659966</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7356,7 +7260,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7366,7 +7270,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7393,10 +7297,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131934963</v>
+        <v>131934907</v>
       </c>
       <c r="B66" t="n">
-        <v>92368</v>
+        <v>99195</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7404,34 +7308,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>634033</v>
+        <v>633997</v>
       </c>
       <c r="R66" t="n">
-        <v>6659947</v>
+        <v>6660017</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -7463,7 +7376,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7473,7 +7386,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7500,10 +7413,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131934960</v>
+        <v>131934909</v>
       </c>
       <c r="B67" t="n">
-        <v>92368</v>
+        <v>99195</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7511,34 +7424,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Enbärsmossarna O, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>633946</v>
+        <v>634018</v>
       </c>
       <c r="R67" t="n">
-        <v>6660010</v>
+        <v>6660002</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -7570,7 +7492,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7580,7 +7502,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7604,6 +7526,1724 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>131934910</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna O, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>634020</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6660000</v>
+      </c>
+      <c r="S68" t="n">
+        <v>8</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>131934911</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna O, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>634020</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6659998</v>
+      </c>
+      <c r="S69" t="n">
+        <v>3</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>131934912</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna O, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>634027</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6659983</v>
+      </c>
+      <c r="S70" t="n">
+        <v>3</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>131934913</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna O, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>634020</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6659988</v>
+      </c>
+      <c r="S71" t="n">
+        <v>3</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>131934915</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna O, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>633972</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6660005</v>
+      </c>
+      <c r="S72" t="n">
+        <v>3</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>131934932</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna O, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>633904</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6660068</v>
+      </c>
+      <c r="S73" t="n">
+        <v>3</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>131934942</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna O, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>633913</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6660082</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>131934943</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna O, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>633915</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6660086</v>
+      </c>
+      <c r="S75" t="n">
+        <v>3</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>131934949</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna O, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>633932</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6660096</v>
+      </c>
+      <c r="S76" t="n">
+        <v>3</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127847518</v>
+      </c>
+      <c r="B77" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>634267</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6659823</v>
+      </c>
+      <c r="S77" t="n">
+        <v>20</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129963923</v>
+      </c>
+      <c r="B78" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>634194</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6659850</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129963925</v>
+      </c>
+      <c r="B79" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>634068</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6660027</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129963926</v>
+      </c>
+      <c r="B80" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>634096</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6659907</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129963927</v>
+      </c>
+      <c r="B81" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>634172</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6659856</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127822935</v>
+      </c>
+      <c r="B82" t="n">
+        <v>80657</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>228430</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Blastenia relicta</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Arup &amp; Vondrák</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>633889</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6660133</v>
+      </c>
+      <c r="S82" t="n">
+        <v>20</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127822933</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>633944</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6660092</v>
+      </c>
+      <c r="S83" t="n">
+        <v>20</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
